--- a/data/쥬스온.xlsx
+++ b/data/쥬스온.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB1DEBC-3DEA-43EE-8316-D204165858AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB437C4-F96D-48AB-9CE7-07B59A4DD234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="210" windowWidth="24150" windowHeight="15480" xr2:uid="{C3FB9D37-16CD-498F-BE3E-EB9B2A1AC5A0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3FB9D37-16CD-498F-BE3E-EB9B2A1AC5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="쥬스온" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>상품번호</t>
   </si>
@@ -182,13 +182,34 @@
   </si>
   <si>
     <t>젤루좋아 맥스 입문 패키지</t>
+  </si>
+  <si>
+    <t>더스페셜 더블그레이프 무니코틴액상 30ml</t>
+  </si>
+  <si>
+    <t>더스페셜 더블포카리 무니코틴액상 30ml</t>
+  </si>
+  <si>
+    <t>더스페셜 더블라임 무니코틴액상 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 딸기밀크 무니코틴액상 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 웰치스 무니코틴액상 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 쿨체리 무니코틴액상 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 파인패션후르츠 무니코틴액상 30ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,6 +368,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="33">
@@ -774,8 +802,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1153,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7AC907-E7B4-4990-AB32-D09188E6DDEA}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1580,6 +1611,62 @@
         <v>12</v>
       </c>
     </row>
+    <row r="54" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>457</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>459</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>460</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>465</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>467</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>468</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>469</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
